--- a/reports/二级子公司D_利润表_2026-09.xlsx
+++ b/reports/二级子公司D_利润表_2026-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>107368494</v>
+        <v>108793524</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>105378401</v>
+        <v>104841437</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>779420929</v>
+        <v>778655546</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>303236</v>
+        <v>304469</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2628160</v>
+        <v>2628962</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>260995</v>
+        <v>261117</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2251685</v>
+        <v>2253921</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>215601</v>
+        <v>217489</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1876148</v>
+        <v>1878422</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>193805</v>
+        <v>195455</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1689379</v>
+        <v>1690440</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>108661</v>
+        <v>108350</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>938512</v>
+        <v>938913</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>86767</v>
+        <v>86464</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>750444</v>
+        <v>750874</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>106199429</v>
+        <v>107620180</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>104209336</v>
+        <v>103668093</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4895949</v>
+        <v>4838098</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>42224297</v>
+        <v>42192251</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>378121</v>
+        <v>376313</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3283097</v>
+        <v>3281123</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>645240</v>
+        <v>645803</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5630662</v>
+        <v>5624843</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>95402737</v>
+        <v>94911021</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>693091758</v>
+        <v>692362793</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1303829</v>
+        <v>1297221</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>11257529</v>
+        <v>11255016</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>430643</v>
+        <v>433486</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3752535</v>
+        <v>3753095</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2156239</v>
+        <v>2172042</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>18771968</v>
+        <v>18772793</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>543764</v>
+        <v>543766</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4692180</v>
+        <v>4694755</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1949140</v>
+        <v>1958368</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16884468</v>
+        <v>16904751</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40953</v>
+        <v>41421</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>370808</v>
+        <v>371164</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1172428</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10142413</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>779870</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6759913</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>59172228</v>
+        <v>62880963</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>53112536</v>
+        <v>52615759</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>52135889</v>
+        <v>51648194</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>450498337</v>
+        <v>450160083</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>976647</v>
+        <v>967565</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>8442629</v>
+        <v>8438207</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1935490</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>16874202</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>620103</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5399924</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>388343</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3375597</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>467157</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4051998</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>351233</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3040168</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>234636</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2027560</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>195778</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1690172</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>915515</v>
+        <v>924762</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>7973936</v>
+        <v>7982940</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>700416</v>
+        <v>706627</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6100777</v>
+        <v>6104837</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>543623</v>
+        <v>542646</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4692328</v>
+        <v>4695442</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4117325</v>
+        <v>4114632</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>35645269</v>
+        <v>35675816</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>153583</v>
+        <v>162011</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1390472</v>
+        <v>1407746</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>329646</v>
+        <v>328413</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2967491</v>
+        <v>2965243</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>372984</v>
+        <v>328413</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3336853</v>
+        <v>2965243</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41113</v>
+        <v>40954</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>370678</v>
+        <v>370447</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>165916</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1500235</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>339196</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2953133</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>110990</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1000568</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83449</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>750713</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139421</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1251719</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>488932</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4224287</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>74589</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>668026</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55950</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>501084</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>93165</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>835094</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>65099</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>584436</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46390</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>417309</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>37019</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>333708</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27702</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>250178</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>47027201</v>
+        <v>45919985</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>51413984</v>
+        <v>49114251</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>193593</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1687408</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46160</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>416798</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>71990</v>
+        <v>71961</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>648676</v>
+        <v>648547</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>46955211</v>
+        <v>46041617</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2583650</v>
+        <v>2582636</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>23181632</v>
+        <v>23181249</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>44371561</v>
+        <v>43458981</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>44371561</v>
+        <v>43458981</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>44371561</v>
+        <v>43458981</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>44371561</v>
+        <v>43458981</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>44371561</v>
+        <v>43458981</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
